--- a/data/registrations.xlsx
+++ b/data/registrations.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>referenceId</t>
   </si>
@@ -44,36 +44,6 @@
   </si>
   <si>
     <t>registrationDateTime</t>
-  </si>
-  <si>
-    <t>TEST-DOWNLOAD-1791352853199</t>
-  </si>
-  <si>
-    <t>EEC/IT/2026-27/AEP/ACTNO.8.</t>
-  </si>
-  <si>
-    <t>SEMINAR</t>
-  </si>
-  <si>
-    <t>Download Test Participant</t>
-  </si>
-  <si>
-    <t>download-test@example.invalid</t>
-  </si>
-  <si>
-    <t>0000000000</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Individual</t>
-  </si>
-  <si>
-    <t>2026-10-07T06:00:53.199Z</t>
   </si>
 </sst>
 </file>
@@ -488,43 +458,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>